--- a/tables/spi_R.xlsx
+++ b/tables/spi_R.xlsx
@@ -13,11 +13,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t xml:space="preserve">nuts2</t>
   </si>
   <si>
+    <t xml:space="preserve">nuts2_label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nuts2_code_label</t>
+  </si>
+  <si>
     <t xml:space="preserve">spi_food</t>
   </si>
   <si>
@@ -39,55 +45,199 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
+    <t xml:space="preserve">dolnoslaskie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1: dolnoslaskie</t>
+  </si>
+  <si>
     <t xml:space="preserve">2</t>
   </si>
   <si>
+    <t xml:space="preserve">kujawsko-pomorskie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2: kujawsko-pomorskie</t>
+  </si>
+  <si>
     <t xml:space="preserve">3</t>
   </si>
   <si>
+    <t xml:space="preserve">lubelskie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3: lubelskie</t>
+  </si>
+  <si>
     <t xml:space="preserve">4</t>
   </si>
   <si>
+    <t xml:space="preserve">lubuskie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4: lubuskie</t>
+  </si>
+  <si>
     <t xml:space="preserve">5</t>
   </si>
   <si>
+    <t xml:space="preserve">lodzkie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5: lodzkie</t>
+  </si>
+  <si>
     <t xml:space="preserve">6</t>
   </si>
   <si>
+    <t xml:space="preserve">malopolskie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6: malopolskie</t>
+  </si>
+  <si>
     <t xml:space="preserve">7</t>
   </si>
   <si>
+    <t xml:space="preserve">mazowieckie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7: mazowieckie</t>
+  </si>
+  <si>
     <t xml:space="preserve">8</t>
   </si>
   <si>
+    <t xml:space="preserve">opolskie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8: opolskie</t>
+  </si>
+  <si>
     <t xml:space="preserve">9</t>
   </si>
   <si>
+    <t xml:space="preserve">podkarpackie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9: podkarpackie</t>
+  </si>
+  <si>
     <t xml:space="preserve">10</t>
   </si>
   <si>
+    <t xml:space="preserve">podlaskie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10: podlaskie</t>
+  </si>
+  <si>
     <t xml:space="preserve">11</t>
   </si>
   <si>
+    <t xml:space="preserve">pomorskie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11: pomorskie</t>
+  </si>
+  <si>
     <t xml:space="preserve">12</t>
   </si>
   <si>
+    <t xml:space="preserve">slaskie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12: slaskie</t>
+  </si>
+  <si>
     <t xml:space="preserve">13</t>
   </si>
   <si>
+    <t xml:space="preserve">swietokrzyskie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13: swietokrzyskie</t>
+  </si>
+  <si>
     <t xml:space="preserve">14</t>
   </si>
   <si>
+    <t xml:space="preserve">warminsko-mazurskie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14: warminsko-mazurskie</t>
+  </si>
+  <si>
     <t xml:space="preserve">15</t>
   </si>
   <si>
+    <t xml:space="preserve">wielkopolskie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15: wielkopolskie</t>
+  </si>
+  <si>
     <t xml:space="preserve">16</t>
   </si>
   <si>
+    <t xml:space="preserve">zachodniopomorskie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16: zachodniopomorskie</t>
+  </si>
+  <si>
     <t xml:space="preserve">34</t>
   </si>
   <si>
+    <t xml:space="preserve">Warsaw metro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34: Warsaw metro</t>
+  </si>
+  <si>
     <t xml:space="preserve">mregion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mregion_label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mregion_code_label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centralny (Central)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1: Centralny (Central)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Południowy (Southern)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2: Południowy (Southern)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wschodni (Eastern)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3: Wschodni (Eastern)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Północno-Zachodni (North-Western)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4: Północno-Zachodni (North-Western)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Południowo-Zachodni (South-Western)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5: Południowo-Zachodni (South-Western)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Północny (Northern)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6: Północny (Northern)</t>
   </si>
 </sst>
 </file>
@@ -438,395 +588,503 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="n">
         <v>1.07258936872129</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>1.07780443184513</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>0.738226608367226</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>1.08949555883816</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>1.10523866849706</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>1.01995766875451</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="n">
         <v>0.944152363309344</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>0.91729015996648</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>0.719423391139615</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>0.959034124977768</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>0.940638695733696</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.993978537968401</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="n">
         <v>0.911245601523706</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>0.808920147707846</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>0.661989019140387</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>0.92560868569345</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>0.829510253026614</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>0.9146253590031</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="n">
         <v>0.99255700225731</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>0.99118374336646</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>0.785897223416367</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>1.00820171949145</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>1.01641315287492</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>1.08582092651646</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="n">
         <v>0.991774723909675</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>0.919735828125771</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>0.654732172994856</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>1.00740711084589</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>0.943146615482489</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>0.904599066543287</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="n">
         <v>0.995197144192938</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>1.09076488555373</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>0.753909405807411</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>1.01088347543408</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>1.11852901522117</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>1.04162552701828</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="n">
         <v>0.844554711671657</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>0.859764271844719</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>0.660998262361357</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>0.857866611766878</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>0.881648554189222</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>0.913256497513703</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="n">
         <v>0.981706965752281</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>0.918027867015646</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>0.957902005959896</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>0.997180664341933</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>0.94139518024301</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>1.3234682762994</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="n">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="n">
         <v>0.905843211507916</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>0.841358062171533</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>0.626080991512336</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>0.920121143022454</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>0.862773836225368</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>0.865013671028206</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="n">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.950078277642072</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>0.89441909866995</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>0.703806390317402</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>0.965053443773794</v>
       </c>
-      <c r="F11" t="n">
+      <c r="H11" t="n">
         <v>0.917185478630834</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>0.972401586432081</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="n">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="n">
         <v>1.01543752881475</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>1.11347657838091</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>0.763077597087416</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>1.03144288968683</v>
       </c>
-      <c r="F12" t="n">
+      <c r="H12" t="n">
         <v>1.14181880731884</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>1.05429259550194</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" t="n">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" t="n">
         <v>1.0017311187316</v>
       </c>
-      <c r="C13" t="n">
+      <c r="E13" t="n">
         <v>0.956020592039339</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>0.75302124210922</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>1.01752043870169</v>
       </c>
-      <c r="F13" t="n">
+      <c r="H13" t="n">
         <v>0.980354965132627</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>1.04039841143505</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" t="n">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="n">
         <v>0.92472586637434</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>0.867571918499449</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>0.611957892740185</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>0.939301426937228</v>
       </c>
-      <c r="F14" t="n">
+      <c r="H14" t="n">
         <v>0.889654935252248</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>0.845500742699744</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" t="n">
+        <v>48</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" t="n">
         <v>0.968372147194644</v>
       </c>
-      <c r="C15" t="n">
+      <c r="E15" t="n">
         <v>0.895709841737771</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>0.643230440032379</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
         <v>0.98363566192057</v>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
         <v>0.918509076036355</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>0.888707901681332</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" t="n">
+        <v>51</v>
+      </c>
+      <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="n">
         <v>0.946127288655206</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>0.951776615044417</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>0.638158624210081</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>0.961040179164113</v>
       </c>
-      <c r="F16" t="n">
+      <c r="H16" t="n">
         <v>0.976002962724388</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>0.881700517520654</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" t="n">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" t="n">
         <v>1.04522074279856</v>
       </c>
-      <c r="C17" t="n">
+      <c r="E17" t="n">
         <v>1.11063649949936</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>0.673804648514923</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>1.06169554770261</v>
       </c>
-      <c r="F17" t="n">
+      <c r="H17" t="n">
         <v>1.13890643758949</v>
       </c>
-      <c r="G17" t="n">
+      <c r="I17" t="n">
         <v>0.930950213262112</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" t="n">
+        <v>57</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" t="n">
         <v>1.24488932973744</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>1.36356542127047</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>0.958071533362871</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>1.2645113177011</v>
       </c>
-      <c r="F18" t="n">
+      <c r="H18" t="n">
         <v>1.39827336582166</v>
       </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
         <v>1.32370250082175</v>
       </c>
     </row>
@@ -843,13 +1101,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -863,142 +1121,184 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" t="n">
         <v>1.07222213790587</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>1.1067717855312</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>0.793525866096654</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>1.0726223719535</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>1.10768820815001</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>1.08728101365583</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" t="n">
         <v>0.998882957944521</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>1.01475565609566</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>0.753408392840024</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>0.999255816287238</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>1.01559588806396</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>1.03231246272209</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="n">
         <v>0.919159074012532</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>0.845400769359949</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>0.649722603925128</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>0.919502173398005</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>0.846100773097965</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>0.890243256802388</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" t="n">
         <v>0.978559071316374</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>0.998232597165645</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>0.67053769343868</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>0.978924343254071</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>0.999059147808548</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>0.918763879245305</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" t="n">
         <v>1.04994069857762</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>1.03798674882518</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>0.792971591512673</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>1.05033261551415</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>1.03884621646529</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>1.08652155229829</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" t="n">
         <v>0.978997244096265</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>0.991888468798924</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>0.718789372224109</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>0.979362679593042</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>0.992709766414231</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>0.984877835276104</v>
       </c>
     </row>
